--- a/Irrigation_log.xlsx
+++ b/Irrigation_log.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/DK/Documents/GitHub/SoilMoisture_analysis/Weather_for_Penman/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/DK/Documents/GitHub/SoilMoisture_analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54DE692B-80F1-DA4C-A423-50EF2A9BC3A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5942B73A-7FBF-3441-8181-4B8F925D2B9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8360" yWindow="15760" windowWidth="31200" windowHeight="15580" xr2:uid="{AFA2ACD8-0CD5-2043-8D59-0A81AC23736D}"/>
   </bookViews>
@@ -451,7 +451,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF4E0D44-5547-8E42-9336-7F1CCC28BE18}">
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
@@ -1335,6 +1335,57 @@
         <v>0</v>
       </c>
       <c r="E52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A53" s="1">
+        <v>45474</v>
+      </c>
+      <c r="B53">
+        <v>0</v>
+      </c>
+      <c r="C53">
+        <v>0</v>
+      </c>
+      <c r="D53">
+        <v>0</v>
+      </c>
+      <c r="E53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A54" s="1">
+        <v>45475</v>
+      </c>
+      <c r="B54">
+        <v>2</v>
+      </c>
+      <c r="C54">
+        <v>0</v>
+      </c>
+      <c r="D54">
+        <v>2</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A55" s="1">
+        <v>45476</v>
+      </c>
+      <c r="B55">
+        <v>0</v>
+      </c>
+      <c r="C55">
+        <v>0</v>
+      </c>
+      <c r="D55">
+        <v>0</v>
+      </c>
+      <c r="E55">
         <v>0</v>
       </c>
     </row>
